--- a/commission/megan/2026-07.xlsx
+++ b/commission/megan/2026-07.xlsx
@@ -5,13 +5,14 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="July 2026-07" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Invoiced This Month" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="76">
   <si>
     <t>Equine Performance Labs, LLC</t>
   </si>
@@ -131,6 +132,114 @@
   </si>
   <si>
     <t>GRAND TOTAL</t>
+  </si>
+  <si>
+    <t>Invoiced This Month — Megan Smith — July 2026</t>
+  </si>
+  <si>
+    <t>Every invoice you wrote this month (paid or unpaid). Commission math comes from Tab 1 — this sheet is for visibility only.</t>
+  </si>
+  <si>
+    <t>INV#</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Vials</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>Commissionable</t>
+  </si>
+  <si>
+    <t>Paid</t>
+  </si>
+  <si>
+    <t>Payment Date</t>
+  </si>
+  <si>
+    <t>Open Bal</t>
+  </si>
+  <si>
+    <t>Promo</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1131</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>SAMPLE26</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1130</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1133</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1139</t>
+  </si>
+  <si>
+    <t>FREE_VIALS</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1142</t>
+  </si>
+  <si>
+    <t>Equine Sports Medicine</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1141</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1146</t>
+  </si>
+  <si>
+    <t>Springhill Equine Veterinary Clinic</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1145</t>
+  </si>
+  <si>
+    <t>Advanced Equine of the Hudson Valley</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1152</t>
+  </si>
+  <si>
+    <t>Ocala Equine Hospital</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1154</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1155</t>
+  </si>
+  <si>
+    <t>Kentucky Equine Medical Associates</t>
+  </si>
+  <si>
+    <t>CINV-EPL-1020</t>
+  </si>
+  <si>
+    <t>ORD-EPL-1156</t>
+  </si>
+  <si>
+    <t>East Fork Equine</t>
+  </si>
+  <si>
+    <t>17 invoices</t>
   </si>
 </sst>
 </file>
@@ -143,7 +252,7 @@
     <numFmt numFmtId="166" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -215,6 +324,42 @@
     <font>
       <b/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="123F35"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="7A7974"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="DA7101"/>
+    </font>
+    <font>
+      <b/>
+    </font>
+    <font>
+      <color rgb="7A7974"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="DA7101"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="123F35"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="0F5E4F"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="7A7974"/>
     </font>
   </fonts>
   <fills count="4">
@@ -247,7 +392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -289,6 +434,45 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1006,4 +1190,755 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="L5" s="27" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="28">
+        <v>46205.5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="29">
+        <v>1</v>
+      </c>
+      <c r="E6" s="19">
+        <v>825</v>
+      </c>
+      <c r="F6" s="30">
+        <v>825</v>
+      </c>
+      <c r="G6" s="31">
+        <v>0</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0</v>
+      </c>
+      <c r="I6" s="32">
+        <v>0</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" s="32">
+        <v>0</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="28">
+        <v>46205.5</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="29">
+        <v>7</v>
+      </c>
+      <c r="E7" s="19">
+        <v>5775</v>
+      </c>
+      <c r="F7" s="30">
+        <v>1575</v>
+      </c>
+      <c r="G7" s="31">
+        <v>4200</v>
+      </c>
+      <c r="H7" s="19">
+        <v>4200</v>
+      </c>
+      <c r="I7" s="21">
+        <v>4200</v>
+      </c>
+      <c r="J7" s="28">
+        <v>46251.5</v>
+      </c>
+      <c r="K7" s="32">
+        <v>0</v>
+      </c>
+      <c r="L7" s="33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="28">
+        <v>46206.5</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="29">
+        <v>1</v>
+      </c>
+      <c r="E8" s="19">
+        <v>825</v>
+      </c>
+      <c r="F8" s="30">
+        <v>825</v>
+      </c>
+      <c r="G8" s="31">
+        <v>0</v>
+      </c>
+      <c r="H8" s="19">
+        <v>0</v>
+      </c>
+      <c r="I8" s="32">
+        <v>0</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8" s="32">
+        <v>0</v>
+      </c>
+      <c r="L8" s="33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="28">
+        <v>46206.5</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="29">
+        <v>1</v>
+      </c>
+      <c r="E9" s="19">
+        <v>825</v>
+      </c>
+      <c r="F9" s="30">
+        <v>225</v>
+      </c>
+      <c r="G9" s="31">
+        <v>600</v>
+      </c>
+      <c r="H9" s="19">
+        <v>600</v>
+      </c>
+      <c r="I9" s="21">
+        <v>617.94</v>
+      </c>
+      <c r="J9" s="28">
+        <v>46209.5</v>
+      </c>
+      <c r="K9" s="32">
+        <v>0</v>
+      </c>
+      <c r="L9" s="33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="28">
+        <v>46217.5</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="29">
+        <v>2</v>
+      </c>
+      <c r="E10" s="19">
+        <v>1650</v>
+      </c>
+      <c r="F10" s="30">
+        <v>1650</v>
+      </c>
+      <c r="G10" s="31">
+        <v>0</v>
+      </c>
+      <c r="H10" s="19">
+        <v>0</v>
+      </c>
+      <c r="I10" s="32">
+        <v>0</v>
+      </c>
+      <c r="J10" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="K10" s="32">
+        <v>0</v>
+      </c>
+      <c r="L10" s="33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="28">
+        <v>46217.5</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="29">
+        <v>8</v>
+      </c>
+      <c r="E11" s="19">
+        <v>6600</v>
+      </c>
+      <c r="F11" s="30">
+        <v>1800</v>
+      </c>
+      <c r="G11" s="31">
+        <v>4800</v>
+      </c>
+      <c r="H11" s="19">
+        <v>4800</v>
+      </c>
+      <c r="I11" s="21">
+        <v>4943.52</v>
+      </c>
+      <c r="J11" s="28">
+        <v>46217.5</v>
+      </c>
+      <c r="K11" s="32">
+        <v>0</v>
+      </c>
+      <c r="L11" s="33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="28">
+        <v>46218.5</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="29">
+        <v>2</v>
+      </c>
+      <c r="E12" s="19">
+        <v>1650</v>
+      </c>
+      <c r="F12" s="30">
+        <v>1650</v>
+      </c>
+      <c r="G12" s="31">
+        <v>0</v>
+      </c>
+      <c r="H12" s="19">
+        <v>0</v>
+      </c>
+      <c r="I12" s="32">
+        <v>0</v>
+      </c>
+      <c r="J12" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="K12" s="32">
+        <v>0</v>
+      </c>
+      <c r="L12" s="33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="28">
+        <v>46218.5</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="29">
+        <v>8</v>
+      </c>
+      <c r="E13" s="19">
+        <v>6600</v>
+      </c>
+      <c r="F13" s="30">
+        <v>1800</v>
+      </c>
+      <c r="G13" s="31">
+        <v>4800</v>
+      </c>
+      <c r="H13" s="19">
+        <v>4800</v>
+      </c>
+      <c r="I13" s="21">
+        <v>4800</v>
+      </c>
+      <c r="J13" s="28">
+        <v>46244.5</v>
+      </c>
+      <c r="K13" s="32">
+        <v>0</v>
+      </c>
+      <c r="L13" s="33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="28">
+        <v>46224.5</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="29">
+        <v>3</v>
+      </c>
+      <c r="E14" s="19">
+        <v>2475</v>
+      </c>
+      <c r="F14" s="30">
+        <v>675</v>
+      </c>
+      <c r="G14" s="31">
+        <v>1800</v>
+      </c>
+      <c r="H14" s="19">
+        <v>1800</v>
+      </c>
+      <c r="I14" s="21">
+        <v>1853.82</v>
+      </c>
+      <c r="J14" s="28">
+        <v>46262.5</v>
+      </c>
+      <c r="K14" s="32">
+        <v>0</v>
+      </c>
+      <c r="L14" s="33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="28">
+        <v>46224.5</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="29">
+        <v>2</v>
+      </c>
+      <c r="E15" s="19">
+        <v>1650</v>
+      </c>
+      <c r="F15" s="30">
+        <v>1650</v>
+      </c>
+      <c r="G15" s="31">
+        <v>0</v>
+      </c>
+      <c r="H15" s="19">
+        <v>0</v>
+      </c>
+      <c r="I15" s="32">
+        <v>0</v>
+      </c>
+      <c r="J15" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" s="32">
+        <v>0</v>
+      </c>
+      <c r="L15" s="33" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="28">
+        <v>46225.5</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="29">
+        <v>1</v>
+      </c>
+      <c r="E16" s="19">
+        <v>825</v>
+      </c>
+      <c r="F16" s="30">
+        <v>225</v>
+      </c>
+      <c r="G16" s="31">
+        <v>600</v>
+      </c>
+      <c r="H16" s="19">
+        <v>600</v>
+      </c>
+      <c r="I16" s="21">
+        <v>617.94</v>
+      </c>
+      <c r="J16" s="28">
+        <v>46226.5</v>
+      </c>
+      <c r="K16" s="32">
+        <v>0</v>
+      </c>
+      <c r="L16" s="33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="28">
+        <v>46226.5</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="29">
+        <v>1</v>
+      </c>
+      <c r="E17" s="19">
+        <v>825</v>
+      </c>
+      <c r="F17" s="30">
+        <v>225</v>
+      </c>
+      <c r="G17" s="31">
+        <v>600</v>
+      </c>
+      <c r="H17" s="19">
+        <v>600</v>
+      </c>
+      <c r="I17" s="21">
+        <v>617.94</v>
+      </c>
+      <c r="J17" s="28">
+        <v>46227.5</v>
+      </c>
+      <c r="K17" s="32">
+        <v>0</v>
+      </c>
+      <c r="L17" s="33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="28">
+        <v>46226.5</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="29">
+        <v>3</v>
+      </c>
+      <c r="E18" s="19">
+        <v>2475</v>
+      </c>
+      <c r="F18" s="30">
+        <v>675</v>
+      </c>
+      <c r="G18" s="31">
+        <v>1800</v>
+      </c>
+      <c r="H18" s="19">
+        <v>1800</v>
+      </c>
+      <c r="I18" s="21">
+        <v>1800</v>
+      </c>
+      <c r="J18" s="28">
+        <v>46259.5</v>
+      </c>
+      <c r="K18" s="32">
+        <v>0</v>
+      </c>
+      <c r="L18" s="33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="28">
+        <v>46229.5</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="29">
+        <v>2</v>
+      </c>
+      <c r="E19" s="19">
+        <v>1650</v>
+      </c>
+      <c r="F19" s="30">
+        <v>1650</v>
+      </c>
+      <c r="G19" s="31">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19">
+        <v>0</v>
+      </c>
+      <c r="I19" s="32">
+        <v>0</v>
+      </c>
+      <c r="J19" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="K19" s="32">
+        <v>0</v>
+      </c>
+      <c r="L19" s="33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="28">
+        <v>46230.5</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="29">
+        <v>1</v>
+      </c>
+      <c r="E20" s="19">
+        <v>825</v>
+      </c>
+      <c r="F20" s="30">
+        <v>825</v>
+      </c>
+      <c r="G20" s="31">
+        <v>0</v>
+      </c>
+      <c r="H20" s="19">
+        <v>0</v>
+      </c>
+      <c r="I20" s="32">
+        <v>0</v>
+      </c>
+      <c r="J20" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="K20" s="32">
+        <v>0</v>
+      </c>
+      <c r="L20" s="33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="28">
+        <v>46231.5</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="29">
+        <v>2</v>
+      </c>
+      <c r="E21" s="19">
+        <v>1200</v>
+      </c>
+      <c r="F21" s="32">
+        <v>0</v>
+      </c>
+      <c r="G21" s="31">
+        <v>1200</v>
+      </c>
+      <c r="H21" s="19">
+        <v>1200</v>
+      </c>
+      <c r="I21" s="21">
+        <v>1200</v>
+      </c>
+      <c r="J21" s="28">
+        <v>46253.5</v>
+      </c>
+      <c r="K21" s="32">
+        <v>0</v>
+      </c>
+      <c r="L21" s="33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B22" s="28">
+        <v>46234.5</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="29">
+        <v>1</v>
+      </c>
+      <c r="E22" s="19">
+        <v>825</v>
+      </c>
+      <c r="F22" s="30">
+        <v>825</v>
+      </c>
+      <c r="G22" s="31">
+        <v>0</v>
+      </c>
+      <c r="H22" s="19">
+        <v>0</v>
+      </c>
+      <c r="I22" s="32">
+        <v>0</v>
+      </c>
+      <c r="J22" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="K22" s="32">
+        <v>0</v>
+      </c>
+      <c r="L22" s="33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="35">
+        <v>46</v>
+      </c>
+      <c r="E24" s="31">
+        <v>37500</v>
+      </c>
+      <c r="F24" s="36">
+        <v>17100</v>
+      </c>
+      <c r="G24" s="37">
+        <v>20400</v>
+      </c>
+      <c r="H24" s="31">
+        <v>20400</v>
+      </c>
+      <c r="I24" s="38">
+        <v>20651.16</v>
+      </c>
+      <c r="K24" s="39">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>